--- a/research/traditional_assets/database/data/bahrain/bahrain_engineering_construction.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_engineering_construction.xlsx
@@ -588,118 +588,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0223</v>
+        <v>-0.073</v>
       </c>
       <c r="G2">
-        <v>0.02054305108967489</v>
+        <v>-0.1137685843568197</v>
       </c>
       <c r="H2">
-        <v>0.02054305108967489</v>
+        <v>-0.1137685843568197</v>
       </c>
       <c r="I2">
-        <v>-0.1446945337620579</v>
+        <v>-0.0345830639948287</v>
       </c>
       <c r="J2">
-        <v>-0.1446945337620579</v>
+        <v>-0.0345830639948287</v>
       </c>
       <c r="K2">
-        <v>-38.8</v>
+        <v>-8.57</v>
       </c>
       <c r="L2">
-        <v>-0.1386209360485888</v>
+        <v>-0.02769877181641888</v>
       </c>
       <c r="M2">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.209</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.1077319587628866</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.209</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.1077319587628866</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>31</v>
+        <v>33.3</v>
       </c>
       <c r="V2">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
-        <v>-0.2730471498944405</v>
+        <v>-0.08288201160541586</v>
       </c>
       <c r="X2">
-        <v>0.3761806647895934</v>
+        <v>0.5067871374426061</v>
       </c>
       <c r="Y2">
-        <v>-0.649227814684034</v>
+        <v>-0.5896691490480219</v>
       </c>
       <c r="Z2">
-        <v>1.506458557588805</v>
+        <v>2.165150454863541</v>
       </c>
       <c r="AA2">
-        <v>-0.2179763186221744</v>
+        <v>-0.0748775367389783</v>
       </c>
       <c r="AB2">
-        <v>0.1437678114471962</v>
+        <v>0.2183639933479847</v>
       </c>
       <c r="AC2">
-        <v>-0.3617441300693706</v>
+        <v>-0.293241530086963</v>
       </c>
       <c r="AD2">
-        <v>70.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>70.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AG2">
-        <v>39.5</v>
+        <v>36.10000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.7790055248618785</v>
+        <v>0.75764192139738</v>
       </c>
       <c r="AI2">
-        <v>0.3951793721973094</v>
+        <v>0.4121140142517815</v>
       </c>
       <c r="AJ2">
-        <v>0.6638655462184874</v>
+        <v>0.6192109777015438</v>
       </c>
       <c r="AK2">
-        <v>0.2679782903663501</v>
+        <v>0.2672094744633605</v>
       </c>
       <c r="AL2">
-        <v>2.97</v>
+        <v>3.26</v>
       </c>
       <c r="AM2">
-        <v>2.784</v>
+        <v>3.003</v>
       </c>
       <c r="AN2">
-        <v>-2.925311203319502</v>
+        <v>-43.1055900621118</v>
       </c>
       <c r="AO2">
-        <v>-13.63636363636363</v>
+        <v>-3.282208588957055</v>
       </c>
       <c r="AP2">
-        <v>-1.639004149377593</v>
+        <v>-22.42236024844721</v>
       </c>
       <c r="AQ2">
-        <v>-14.54741379310345</v>
+        <v>-3.563103563103563</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +716,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0223</v>
+        <v>-0.073</v>
       </c>
       <c r="G3">
-        <v>0.02054305108967489</v>
+        <v>-0.1137685843568197</v>
       </c>
       <c r="H3">
-        <v>0.02054305108967489</v>
+        <v>-0.1137685843568197</v>
       </c>
       <c r="I3">
-        <v>-0.1446945337620579</v>
+        <v>-0.0345830639948287</v>
       </c>
       <c r="J3">
-        <v>-0.1446945337620579</v>
+        <v>-0.0345830639948287</v>
       </c>
       <c r="K3">
-        <v>-38.8</v>
+        <v>-8.57</v>
       </c>
       <c r="L3">
-        <v>-0.1386209360485888</v>
+        <v>-0.02769877181641888</v>
       </c>
       <c r="M3">
-        <v>4.18</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.209</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.1077319587628866</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>4.18</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.209</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0.1077319587628866</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>31</v>
+        <v>33.3</v>
       </c>
       <c r="V3">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>-0.2730471498944405</v>
+        <v>-0.08288201160541586</v>
       </c>
       <c r="X3">
-        <v>0.3761806647895934</v>
+        <v>0.5067871374426061</v>
       </c>
       <c r="Y3">
-        <v>-0.649227814684034</v>
+        <v>-0.5896691490480219</v>
       </c>
       <c r="Z3">
-        <v>1.506458557588805</v>
+        <v>2.165150454863541</v>
       </c>
       <c r="AA3">
-        <v>-0.2179763186221744</v>
+        <v>-0.0748775367389783</v>
       </c>
       <c r="AB3">
-        <v>0.1437678114471962</v>
+        <v>0.2183639933479847</v>
       </c>
       <c r="AC3">
-        <v>-0.3617441300693706</v>
+        <v>-0.293241530086963</v>
       </c>
       <c r="AD3">
-        <v>70.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>70.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AG3">
-        <v>39.5</v>
+        <v>36.10000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.7790055248618785</v>
+        <v>0.75764192139738</v>
       </c>
       <c r="AI3">
-        <v>0.3951793721973094</v>
+        <v>0.4121140142517815</v>
       </c>
       <c r="AJ3">
-        <v>0.6638655462184874</v>
+        <v>0.6192109777015438</v>
       </c>
       <c r="AK3">
-        <v>0.2679782903663501</v>
+        <v>0.2672094744633605</v>
       </c>
       <c r="AL3">
-        <v>2.97</v>
+        <v>3.26</v>
       </c>
       <c r="AM3">
-        <v>2.784</v>
+        <v>3.003</v>
       </c>
       <c r="AN3">
-        <v>-2.925311203319502</v>
+        <v>-43.1055900621118</v>
       </c>
       <c r="AO3">
-        <v>-13.63636363636363</v>
+        <v>-3.282208588957055</v>
       </c>
       <c r="AP3">
-        <v>-1.639004149377593</v>
+        <v>-22.42236024844721</v>
       </c>
       <c r="AQ3">
-        <v>-14.54741379310345</v>
+        <v>-3.563103563103563</v>
       </c>
     </row>
   </sheetData>
